--- a/data/trans_dic/Predimed_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 12,57</t>
+          <t>2,95; 12,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 18,74</t>
+          <t>7,96; 18,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 13,31</t>
+          <t>6,12; 13,73</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 18,51</t>
+          <t>7,74; 18,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 17,67</t>
+          <t>10,66; 17,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 23,47</t>
+          <t>15,09; 22,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 20,54</t>
+          <t>15,11; 20,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,1; 20,68</t>
+          <t>16,02; 20,76</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 18,49</t>
+          <t>5,36; 18,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 38,09</t>
+          <t>20,66; 38,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 23,51</t>
+          <t>11,13; 23,95</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,02; 22,48</t>
+          <t>15,43; 22,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,31; 22,7</t>
+          <t>17,32; 22,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,75</t>
+          <t>17,48; 21,66</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,58; 28,95</t>
+          <t>21,41; 29,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 26,71</t>
+          <t>6,29; 26,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,91; 26,3</t>
+          <t>10,11; 26,35</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 22,86</t>
+          <t>14,91; 22,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 20,01</t>
+          <t>14,43; 20,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 20,02</t>
+          <t>15,36; 19,98</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,89</t>
+          <t>12,29; 17,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,03</t>
+          <t>14,88; 20,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 18,94</t>
+          <t>14,75; 18,82</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9967; 43290</t>
+          <t>10155; 42933</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22337; 52259</t>
+          <t>22213; 51615</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38049; 82991</t>
+          <t>38129; 85575</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42213; 82704</t>
+          <t>42239; 82731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42218; 89211</t>
+          <t>37298; 86778</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94561; 156542</t>
+          <t>94479; 157360</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78639; 119435</t>
+          <t>76813; 114117</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76873; 106295</t>
+          <t>78198; 108161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165228; 212225</t>
+          <t>164441; 213002</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47681; 157294</t>
+          <t>45632; 154942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>139579; 260510</t>
+          <t>141313; 264684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177701; 360832</t>
+          <t>170800; 367640</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83771; 117512</t>
+          <t>80646; 116358</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90101; 118155</t>
+          <t>90134; 116094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183760; 226866</t>
+          <t>182315; 225909</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73271; 98303</t>
+          <t>72695; 99682</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37214; 158175</t>
+          <t>37247; 157507</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92369; 245101</t>
+          <t>94249; 245507</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37616; 58485</t>
+          <t>38152; 58020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56664; 77395</t>
+          <t>55801; 77910</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99809; 128660</t>
+          <t>98714; 128401</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>390986; 577176</t>
+          <t>396623; 579041</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>515200; 727904</t>
+          <t>515132; 721511</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>990921; 1266726</t>
+          <t>986434; 1258894</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,46</t>
+          <t>2,99; 12,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 18,5</t>
+          <t>8,84; 19,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,73</t>
+          <t>6,89; 13,63</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,47</t>
+          <t>11,79; 20,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 18,0</t>
+          <t>12,29; 20,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 17,76</t>
+          <t>13,23; 19,21</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 22,43</t>
+          <t>14,91; 21,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 20,91</t>
+          <t>15,14; 20,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,02; 20,76</t>
+          <t>15,83; 20,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 18,21</t>
+          <t>14,87; 20,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,66; 38,7</t>
+          <t>18,28; 23,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,13; 23,95</t>
+          <t>17,42; 21,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 22,26</t>
+          <t>16,21; 22,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 22,31</t>
+          <t>17,37; 22,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,48; 21,66</t>
+          <t>17,57; 21,79</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,41; 29,36</t>
+          <t>22,53; 29,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 26,59</t>
+          <t>22,55; 28,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 26,35</t>
+          <t>23,52; 28,37</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,91; 22,68</t>
+          <t>14,76; 22,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 20,14</t>
+          <t>14,77; 20,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,36; 19,98</t>
+          <t>15,51; 20,12</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,95</t>
+          <t>16,28; 19,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 20,84</t>
+          <t>17,82; 20,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,82</t>
+          <t>17,31; 19,3</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57197</t>
+          <t>66657</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10155; 42933</t>
+          <t>10601; 43947</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22213; 51615</t>
+          <t>28874; 63014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38129; 85575</t>
+          <t>46910; 92768</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>61466</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66799</t>
+          <t>73126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128265</t>
+          <t>145917</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42239; 82731</t>
+          <t>53301; 94390</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37298; 86778</t>
+          <t>57060; 92893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94479; 157360</t>
+          <t>121263; 176066</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95670</t>
+          <t>106899</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91695</t>
+          <t>104696</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187365</t>
+          <t>211595</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76813; 114117</t>
+          <t>87530; 128612</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78198; 108161</t>
+          <t>89623; 120795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164441; 213002</t>
+          <t>186629; 237994</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>104996</t>
+          <t>115984</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173336</t>
+          <t>146792</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>262776</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45632; 154942</t>
+          <t>98170; 138558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141313; 264684</t>
+          <t>129126; 164209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170800; 367640</t>
+          <t>238044; 289594</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>99785</t>
+          <t>109213</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>102804</t>
+          <t>114575</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202589</t>
+          <t>223788</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80646; 116358</t>
+          <t>92114; 129067</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90134; 116094</t>
+          <t>100543; 129806</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182315; 225909</t>
+          <t>201531; 249854</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>97976</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>99763</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185106</t>
+          <t>205278</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72695; 99682</t>
+          <t>84728; 112662</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37247; 157507</t>
+          <t>94951; 119856</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94249; 245507</t>
+          <t>187517; 226179</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>46917</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112982</t>
+          <t>125652</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38152; 58020</t>
+          <t>41295; 62849</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55801; 77910</t>
+          <t>62397; 86900</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98714; 128401</t>
+          <t>108919; 141350</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>396623; 579041</t>
+          <t>533687; 631365</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>515132; 721511</t>
+          <t>625674; 707948</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>986434; 1258894</t>
+          <t>1175345; 1310511</t>
         </is>
       </c>
     </row>
